--- a/docs/assets_output/04_bivariate_analysis_placements.xlsx
+++ b/docs/assets_output/04_bivariate_analysis_placements.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R124"/>
+  <dimension ref="A1:R127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,165 +818,138 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" s="1" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>277</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>Died</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B25" t="n">
         <v>117</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C25" t="n">
         <v>1.9</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Table 4.3: Placement outcomes by pathway type and level</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>pathway_type</t>
-        </is>
-      </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>Homelessness</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="n"/>
-      <c r="D27" s="1" t="n"/>
-      <c r="E27" s="1" t="n"/>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>Substance Misuse</t>
-        </is>
-      </c>
-      <c r="G27" s="1" t="n"/>
-      <c r="H27" s="1" t="n"/>
-      <c r="I27" s="1" t="n"/>
-      <c r="J27" s="1" t="inlineStr">
-        <is>
-          <t>All</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>pathway_level</t>
+          <t>pathway_type</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E28" s="1" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Homelessness</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="n"/>
+      <c r="D28" s="1" t="n"/>
+      <c r="E28" s="1" t="n"/>
       <c r="F28" s="1" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G28" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H28" s="1" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I28" s="1" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J28" s="1" t="inlineStr"/>
+          <t>Substance Misuse</t>
+        </is>
+      </c>
+      <c r="G28" s="1" t="n"/>
+      <c r="H28" s="1" t="n"/>
+      <c r="I28" s="1" t="n"/>
+      <c r="J28" s="1" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>pl_outcome</t>
-        </is>
-      </c>
+          <t>pathway_level</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H29" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I29" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J29" s="1" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Internal move: forwards</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>924</v>
-      </c>
-      <c r="C30" t="n">
-        <v>301</v>
-      </c>
-      <c r="D30" t="n">
-        <v>88</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>212</v>
-      </c>
-      <c r="G30" t="n">
-        <v>37</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1562</v>
+          <t>pl_outcome</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Independent accommodation</t>
+          <t>Internal move: forwards</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>153</v>
+        <v>924</v>
       </c>
       <c r="C31" t="n">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="D31" t="n">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="E31" t="n">
-        <v>738</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>48</v>
+        <v>212</v>
       </c>
       <c r="G31" t="n">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -985,32 +958,32 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1225</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Internal move: sideways</t>
+          <t>Independent accommodation</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>705</v>
+        <v>153</v>
       </c>
       <c r="C32" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="D32" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="E32" t="n">
-        <v>33</v>
+        <v>738</v>
       </c>
       <c r="F32" t="n">
-        <v>342</v>
+        <v>48</v>
       </c>
       <c r="G32" t="n">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1019,32 +992,32 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>1164</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>Returned to homelessness</t>
+          <t>Internal move: sideways</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>362</v>
+        <v>705</v>
       </c>
       <c r="C33" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D33" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="E33" t="n">
-        <v>92</v>
+        <v>33</v>
       </c>
       <c r="F33" t="n">
-        <v>168</v>
+        <v>342</v>
       </c>
       <c r="G33" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1053,32 +1026,32 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>744</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Internal move: backwards</t>
+          <t>Returned to homelessness</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>362</v>
       </c>
       <c r="C34" t="n">
-        <v>218</v>
+        <v>70</v>
       </c>
       <c r="D34" t="n">
-        <v>116</v>
+        <v>31</v>
       </c>
       <c r="E34" t="n">
-        <v>191</v>
+        <v>92</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="G34" t="n">
-        <v>128</v>
+        <v>21</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1087,32 +1060,32 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>653</v>
+        <v>744</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Insecure outcome</t>
+          <t>Internal move: backwards</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>284</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>85</v>
+        <v>218</v>
       </c>
       <c r="D35" t="n">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="E35" t="n">
-        <v>113</v>
+        <v>191</v>
       </c>
       <c r="F35" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>25</v>
+        <v>128</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1121,32 +1094,32 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>638</v>
+        <v>653</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Died</t>
+          <t>Insecure outcome</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>48</v>
+        <v>284</v>
       </c>
       <c r="C36" t="n">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="D36" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E36" t="n">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="F36" t="n">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1155,1524 +1128,1440 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>117</v>
+        <v>638</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
+          <t>Died</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>48</v>
+      </c>
+      <c r="C37" t="n">
+        <v>19</v>
+      </c>
+      <c r="D37" t="n">
+        <v>11</v>
+      </c>
+      <c r="E37" t="n">
+        <v>23</v>
+      </c>
+      <c r="F37" t="n">
+        <v>14</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr"/>
+      <c r="B38" t="n">
+        <v>68</v>
+      </c>
+      <c r="C38" t="n">
+        <v>38</v>
+      </c>
+      <c r="D38" t="n">
+        <v>25</v>
+      </c>
+      <c r="E38" t="n">
+        <v>78</v>
+      </c>
+      <c r="F38" t="n">
+        <v>51</v>
+      </c>
+      <c r="G38" t="n">
+        <v>17</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>2476</v>
-      </c>
-      <c r="C37" t="n">
-        <v>843</v>
-      </c>
-      <c r="D37" t="n">
-        <v>413</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1190</v>
-      </c>
-      <c r="F37" t="n">
-        <v>880</v>
-      </c>
-      <c r="G37" t="n">
-        <v>301</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="n">
-        <v>6103</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="B39" t="n">
+        <v>2544</v>
+      </c>
+      <c r="C39" t="n">
+        <v>881</v>
+      </c>
+      <c r="D39" t="n">
+        <v>438</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1268</v>
+      </c>
+      <c r="F39" t="n">
+        <v>931</v>
+      </c>
+      <c r="G39" t="n">
+        <v>318</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>6380</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Table 4.4: Placement outcomes (as row percentages) by pathway type and level</t>
         </is>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>pathway_type</t>
-        </is>
-      </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>Homelessness</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="n"/>
-      <c r="D40" s="1" t="n"/>
-      <c r="E40" s="1" t="n"/>
-      <c r="F40" s="1" t="inlineStr">
-        <is>
-          <t>Substance Misuse</t>
-        </is>
-      </c>
-      <c r="G40" s="1" t="n"/>
-      <c r="H40" s="1" t="n"/>
-      <c r="I40" s="1" t="n"/>
-      <c r="J40" s="1" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>pathway_level</t>
-        </is>
-      </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E41" s="1" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F41" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G41" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H41" s="1" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I41" s="1" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J41" s="1" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>pl_outcome</t>
+          <t>pathway_type</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>Homelessness</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="n"/>
+      <c r="D42" s="1" t="n"/>
+      <c r="E42" s="1" t="n"/>
+      <c r="F42" s="1" t="inlineStr">
+        <is>
+          <t>Substance Misuse</t>
+        </is>
+      </c>
+      <c r="G42" s="1" t="n"/>
+      <c r="H42" s="1" t="n"/>
+      <c r="I42" s="1" t="n"/>
+      <c r="J42" s="1" t="inlineStr">
+        <is>
+          <t>All</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>Internal move: forwards</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="C43" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="D43" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="G43" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="n">
-        <v>25.6</v>
-      </c>
+          <t>pathway_level</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F43" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G43" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H43" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I43" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J43" s="1" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>Independent accommodation</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="C44" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="D44" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="E44" t="n">
-        <v>62</v>
-      </c>
-      <c r="F44" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G44" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="n">
-        <v>20.1</v>
+          <t>pl_outcome</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Internal move: sideways</t>
+          <t>Internal move: forwards</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>28.5</v>
+        <v>36.3</v>
       </c>
       <c r="C45" t="n">
-        <v>8.1</v>
+        <v>34.2</v>
       </c>
       <c r="D45" t="n">
-        <v>2.9</v>
+        <v>20.1</v>
       </c>
       <c r="E45" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>38.9</v>
+        <v>22.8</v>
       </c>
       <c r="G45" t="n">
-        <v>1.3</v>
+        <v>11.6</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>19.1</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>Returned to homelessness</t>
+          <t>Independent accommodation</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>14.6</v>
+        <v>6</v>
       </c>
       <c r="C46" t="n">
-        <v>8.300000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>7.5</v>
+        <v>27.4</v>
       </c>
       <c r="E46" t="n">
-        <v>7.7</v>
+        <v>58.2</v>
       </c>
       <c r="F46" t="n">
-        <v>19.1</v>
+        <v>5.2</v>
       </c>
       <c r="G46" t="n">
-        <v>7</v>
+        <v>26.4</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>12.2</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>Internal move: backwards</t>
+          <t>Internal move: sideways</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>27.7</v>
       </c>
       <c r="C47" t="n">
-        <v>25.9</v>
+        <v>7.7</v>
       </c>
       <c r="D47" t="n">
-        <v>28.1</v>
+        <v>2.7</v>
       </c>
       <c r="E47" t="n">
-        <v>16.1</v>
+        <v>2.6</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>36.7</v>
       </c>
       <c r="G47" t="n">
-        <v>42.5</v>
+        <v>1.3</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
-        <v>10.7</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>Insecure outcome</t>
+          <t>Returned to homelessness</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>11.5</v>
+        <v>14.2</v>
       </c>
       <c r="C48" t="n">
-        <v>10.1</v>
+        <v>7.9</v>
       </c>
       <c r="D48" t="n">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="E48" t="n">
-        <v>9.5</v>
+        <v>7.3</v>
       </c>
       <c r="F48" t="n">
-        <v>10.9</v>
+        <v>18</v>
       </c>
       <c r="G48" t="n">
-        <v>8.300000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
-        <v>10.5</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>Died</t>
+          <t>Internal move: backwards</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>2.3</v>
+        <v>24.7</v>
       </c>
       <c r="D49" t="n">
-        <v>2.7</v>
+        <v>26.5</v>
       </c>
       <c r="E49" t="n">
-        <v>1.9</v>
+        <v>15.1</v>
       </c>
       <c r="F49" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0.7</v>
+        <v>40.3</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="n">
-        <v>1.9</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Insecure outcome</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>100</v>
+        <v>11.2</v>
       </c>
       <c r="C50" t="n">
-        <v>100</v>
+        <v>9.6</v>
       </c>
       <c r="D50" t="n">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="E50" t="n">
-        <v>100</v>
+        <v>8.9</v>
       </c>
       <c r="F50" t="n">
-        <v>100</v>
+        <v>10.3</v>
       </c>
       <c r="G50" t="n">
-        <v>100</v>
+        <v>7.9</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
-        <v>100</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>Died</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C51" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="n">
+        <v>1.8</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Table 4.5: Placement outcomes by calendar year</t>
-        </is>
-      </c>
+      <c r="A52" s="1" t="inlineStr"/>
+      <c r="B52" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C52" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D52" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="E52" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F52" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G52" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>pl_outcome</t>
-        </is>
-      </c>
-      <c r="B53" s="1" t="n">
-        <v>2017</v>
-      </c>
-      <c r="C53" s="1" t="n">
-        <v>2018</v>
-      </c>
-      <c r="D53" s="1" t="n">
-        <v>2019</v>
-      </c>
-      <c r="E53" s="1" t="n">
-        <v>2020</v>
-      </c>
-      <c r="F53" s="1" t="n">
-        <v>2021</v>
-      </c>
-      <c r="G53" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="H53" s="1" t="n">
-        <v>2023</v>
-      </c>
-      <c r="I53" s="1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="J53" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
           <t>All</t>
         </is>
       </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>Internal move: forwards</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>60</v>
-      </c>
-      <c r="C54" t="n">
-        <v>341</v>
-      </c>
-      <c r="D54" t="n">
-        <v>298</v>
-      </c>
-      <c r="E54" t="n">
-        <v>228</v>
-      </c>
-      <c r="F54" t="n">
-        <v>196</v>
-      </c>
-      <c r="G54" t="n">
-        <v>166</v>
-      </c>
-      <c r="H54" t="n">
-        <v>112</v>
-      </c>
-      <c r="I54" t="n">
-        <v>120</v>
-      </c>
-      <c r="J54" t="n">
-        <v>41</v>
-      </c>
-      <c r="K54" t="n">
-        <v>1562</v>
+      <c r="B53" t="n">
+        <v>100</v>
+      </c>
+      <c r="C53" t="n">
+        <v>100</v>
+      </c>
+      <c r="D53" t="n">
+        <v>100</v>
+      </c>
+      <c r="E53" t="n">
+        <v>100</v>
+      </c>
+      <c r="F53" t="n">
+        <v>100</v>
+      </c>
+      <c r="G53" t="n">
+        <v>100</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>Independent accommodation</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>40</v>
-      </c>
-      <c r="C55" t="n">
-        <v>198</v>
-      </c>
-      <c r="D55" t="n">
-        <v>189</v>
-      </c>
-      <c r="E55" t="n">
-        <v>229</v>
-      </c>
-      <c r="F55" t="n">
-        <v>162</v>
-      </c>
-      <c r="G55" t="n">
-        <v>156</v>
-      </c>
-      <c r="H55" t="n">
-        <v>96</v>
-      </c>
-      <c r="I55" t="n">
-        <v>118</v>
-      </c>
-      <c r="J55" t="n">
-        <v>37</v>
-      </c>
-      <c r="K55" t="n">
-        <v>1225</v>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Table 4.5: Placement outcomes by calendar year</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>Internal move: sideways</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>33</v>
-      </c>
-      <c r="C56" t="n">
-        <v>189</v>
-      </c>
-      <c r="D56" t="n">
-        <v>206</v>
-      </c>
-      <c r="E56" t="n">
-        <v>170</v>
-      </c>
-      <c r="F56" t="n">
-        <v>189</v>
-      </c>
-      <c r="G56" t="n">
-        <v>116</v>
-      </c>
-      <c r="H56" t="n">
-        <v>130</v>
-      </c>
-      <c r="I56" t="n">
-        <v>100</v>
-      </c>
-      <c r="J56" t="n">
-        <v>31</v>
-      </c>
-      <c r="K56" t="n">
-        <v>1164</v>
+          <t>pl_outcome</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C56" s="1" t="n">
+        <v>2018</v>
+      </c>
+      <c r="D56" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E56" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F56" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G56" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="H56" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="I56" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="J56" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K56" s="1" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>Returned to homelessness</t>
+          <t>Internal move: forwards</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="C57" t="n">
-        <v>51</v>
+        <v>341</v>
       </c>
       <c r="D57" t="n">
-        <v>85</v>
+        <v>298</v>
       </c>
       <c r="E57" t="n">
-        <v>72</v>
+        <v>228</v>
       </c>
       <c r="F57" t="n">
-        <v>95</v>
+        <v>196</v>
       </c>
       <c r="G57" t="n">
-        <v>114</v>
+        <v>166</v>
       </c>
       <c r="H57" t="n">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="I57" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="J57" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="K57" t="n">
-        <v>744</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>Internal move: backwards</t>
+          <t>Independent accommodation</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C58" t="n">
-        <v>124</v>
+        <v>198</v>
       </c>
       <c r="D58" t="n">
-        <v>126</v>
+        <v>189</v>
       </c>
       <c r="E58" t="n">
-        <v>81</v>
+        <v>229</v>
       </c>
       <c r="F58" t="n">
-        <v>78</v>
+        <v>162</v>
       </c>
       <c r="G58" t="n">
-        <v>66</v>
+        <v>156</v>
       </c>
       <c r="H58" t="n">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="I58" t="n">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="J58" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="K58" t="n">
-        <v>653</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>Insecure outcome</t>
+          <t>Internal move: sideways</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="C59" t="n">
-        <v>96</v>
+        <v>189</v>
       </c>
       <c r="D59" t="n">
-        <v>87</v>
+        <v>206</v>
       </c>
       <c r="E59" t="n">
-        <v>82</v>
+        <v>170</v>
       </c>
       <c r="F59" t="n">
-        <v>95</v>
+        <v>189</v>
       </c>
       <c r="G59" t="n">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="H59" t="n">
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="I59" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="J59" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="K59" t="n">
-        <v>638</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>Died</t>
+          <t>Returned to homelessness</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C60" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="D60" t="n">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="E60" t="n">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="F60" t="n">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="G60" t="n">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="H60" t="n">
-        <v>14</v>
+        <v>127</v>
       </c>
       <c r="I60" t="n">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="J60" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="K60" t="n">
-        <v>117</v>
+        <v>744</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Internal move: backwards</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>190</v>
+        <v>28</v>
       </c>
       <c r="C61" t="n">
-        <v>1016</v>
+        <v>124</v>
       </c>
       <c r="D61" t="n">
-        <v>1008</v>
+        <v>126</v>
       </c>
       <c r="E61" t="n">
-        <v>878</v>
+        <v>81</v>
       </c>
       <c r="F61" t="n">
-        <v>835</v>
+        <v>78</v>
       </c>
       <c r="G61" t="n">
-        <v>717</v>
+        <v>66</v>
       </c>
       <c r="H61" t="n">
-        <v>624</v>
+        <v>73</v>
       </c>
       <c r="I61" t="n">
-        <v>619</v>
+        <v>62</v>
       </c>
       <c r="J61" t="n">
-        <v>216</v>
+        <v>15</v>
       </c>
       <c r="K61" t="n">
-        <v>6103</v>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>Insecure outcome</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>13</v>
+      </c>
+      <c r="C62" t="n">
+        <v>96</v>
+      </c>
+      <c r="D62" t="n">
+        <v>87</v>
+      </c>
+      <c r="E62" t="n">
+        <v>82</v>
+      </c>
+      <c r="F62" t="n">
+        <v>95</v>
+      </c>
+      <c r="G62" t="n">
+        <v>86</v>
+      </c>
+      <c r="H62" t="n">
+        <v>72</v>
+      </c>
+      <c r="I62" t="n">
+        <v>67</v>
+      </c>
+      <c r="J62" t="n">
+        <v>40</v>
+      </c>
+      <c r="K62" t="n">
+        <v>638</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Table 4.6: Placement outcomes (as row percentages) by calendar year</t>
-        </is>
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>Died</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" t="n">
+        <v>17</v>
+      </c>
+      <c r="D63" t="n">
+        <v>17</v>
+      </c>
+      <c r="E63" t="n">
+        <v>16</v>
+      </c>
+      <c r="F63" t="n">
+        <v>20</v>
+      </c>
+      <c r="G63" t="n">
+        <v>13</v>
+      </c>
+      <c r="H63" t="n">
+        <v>14</v>
+      </c>
+      <c r="I63" t="n">
+        <v>15</v>
+      </c>
+      <c r="J63" t="n">
+        <v>3</v>
+      </c>
+      <c r="K63" t="n">
+        <v>117</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>pl_outcome</t>
-        </is>
-      </c>
-      <c r="B64" s="1" t="n">
-        <v>2017</v>
-      </c>
-      <c r="C64" s="1" t="n">
-        <v>2018</v>
-      </c>
-      <c r="D64" s="1" t="n">
-        <v>2019</v>
-      </c>
-      <c r="E64" s="1" t="n">
-        <v>2020</v>
-      </c>
-      <c r="F64" s="1" t="n">
-        <v>2021</v>
-      </c>
-      <c r="G64" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="H64" s="1" t="n">
-        <v>2023</v>
-      </c>
-      <c r="I64" s="1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="J64" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
           <t>All</t>
         </is>
       </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="1" t="inlineStr">
-        <is>
-          <t>Internal move: forwards</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="C65" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="D65" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="E65" t="n">
-        <v>26</v>
-      </c>
-      <c r="F65" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G65" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="H65" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="I65" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="J65" t="n">
-        <v>19</v>
-      </c>
-      <c r="K65" t="n">
-        <v>25.6</v>
+      <c r="B64" t="n">
+        <v>190</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1016</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1008</v>
+      </c>
+      <c r="E64" t="n">
+        <v>878</v>
+      </c>
+      <c r="F64" t="n">
+        <v>835</v>
+      </c>
+      <c r="G64" t="n">
+        <v>717</v>
+      </c>
+      <c r="H64" t="n">
+        <v>624</v>
+      </c>
+      <c r="I64" t="n">
+        <v>619</v>
+      </c>
+      <c r="J64" t="n">
+        <v>216</v>
+      </c>
+      <c r="K64" t="n">
+        <v>6103</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="inlineStr">
-        <is>
-          <t>Independent accommodation</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="C66" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="D66" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="E66" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="F66" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="G66" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H66" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="I66" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="J66" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="K66" t="n">
-        <v>20.1</v>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Table 4.6: Placement outcomes (as row percentages) by calendar year</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>Internal move: sideways</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="C67" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="D67" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="E67" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F67" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="G67" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="H67" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="I67" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="J67" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="K67" t="n">
-        <v>19.1</v>
+          <t>pl_outcome</t>
+        </is>
+      </c>
+      <c r="B67" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C67" s="1" t="n">
+        <v>2018</v>
+      </c>
+      <c r="D67" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E67" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F67" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G67" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="H67" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="I67" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="J67" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K67" s="1" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>Returned to homelessness</t>
+          <t>Internal move: forwards</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>7.4</v>
+        <v>31.6</v>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>33.6</v>
       </c>
       <c r="D68" t="n">
-        <v>8.4</v>
+        <v>29.6</v>
       </c>
       <c r="E68" t="n">
-        <v>8.199999999999999</v>
+        <v>26</v>
       </c>
       <c r="F68" t="n">
-        <v>11.4</v>
+        <v>23.5</v>
       </c>
       <c r="G68" t="n">
-        <v>15.9</v>
+        <v>23.2</v>
       </c>
       <c r="H68" t="n">
-        <v>20.4</v>
+        <v>17.9</v>
       </c>
       <c r="I68" t="n">
-        <v>22.1</v>
+        <v>19.4</v>
       </c>
       <c r="J68" t="n">
-        <v>22.7</v>
+        <v>19</v>
       </c>
       <c r="K68" t="n">
-        <v>12.2</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>Internal move: backwards</t>
+          <t>Independent accommodation</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>14.7</v>
+        <v>21.1</v>
       </c>
       <c r="C69" t="n">
-        <v>12.2</v>
+        <v>19.5</v>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>18.8</v>
       </c>
       <c r="E69" t="n">
-        <v>9.199999999999999</v>
+        <v>26.1</v>
       </c>
       <c r="F69" t="n">
-        <v>9.300000000000001</v>
+        <v>19.4</v>
       </c>
       <c r="G69" t="n">
-        <v>9.199999999999999</v>
+        <v>21.8</v>
       </c>
       <c r="H69" t="n">
-        <v>11.7</v>
+        <v>15.4</v>
       </c>
       <c r="I69" t="n">
-        <v>10</v>
+        <v>19.1</v>
       </c>
       <c r="J69" t="n">
-        <v>6.9</v>
+        <v>17.1</v>
       </c>
       <c r="K69" t="n">
-        <v>10.7</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>Insecure outcome</t>
+          <t>Internal move: sideways</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>6.8</v>
+        <v>17.4</v>
       </c>
       <c r="C70" t="n">
-        <v>9.4</v>
+        <v>18.6</v>
       </c>
       <c r="D70" t="n">
-        <v>8.6</v>
+        <v>20.4</v>
       </c>
       <c r="E70" t="n">
-        <v>9.300000000000001</v>
+        <v>19.4</v>
       </c>
       <c r="F70" t="n">
-        <v>11.4</v>
+        <v>22.6</v>
       </c>
       <c r="G70" t="n">
-        <v>12</v>
+        <v>16.2</v>
       </c>
       <c r="H70" t="n">
-        <v>11.5</v>
+        <v>20.8</v>
       </c>
       <c r="I70" t="n">
-        <v>10.8</v>
+        <v>16.2</v>
       </c>
       <c r="J70" t="n">
-        <v>18.5</v>
+        <v>14.4</v>
       </c>
       <c r="K70" t="n">
-        <v>10.5</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>Died</t>
+          <t>Returned to homelessness</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1.1</v>
+        <v>7.4</v>
       </c>
       <c r="C71" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="D71" t="n">
-        <v>1.7</v>
+        <v>8.4</v>
       </c>
       <c r="E71" t="n">
-        <v>1.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F71" t="n">
-        <v>2.4</v>
+        <v>11.4</v>
       </c>
       <c r="G71" t="n">
-        <v>1.8</v>
+        <v>15.9</v>
       </c>
       <c r="H71" t="n">
-        <v>2.2</v>
+        <v>20.4</v>
       </c>
       <c r="I71" t="n">
-        <v>2.4</v>
+        <v>22.1</v>
       </c>
       <c r="J71" t="n">
-        <v>1.4</v>
+        <v>22.7</v>
       </c>
       <c r="K71" t="n">
-        <v>1.9</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Internal move: backwards</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>100</v>
+        <v>14.7</v>
       </c>
       <c r="C72" t="n">
-        <v>100</v>
+        <v>12.2</v>
       </c>
       <c r="D72" t="n">
-        <v>100</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="n">
-        <v>100</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F72" t="n">
-        <v>100</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G72" t="n">
-        <v>100</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H72" t="n">
-        <v>100</v>
+        <v>11.7</v>
       </c>
       <c r="I72" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="J72" t="n">
-        <v>100</v>
+        <v>6.9</v>
       </c>
       <c r="K72" t="n">
-        <v>100</v>
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>Insecure outcome</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C73" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="D73" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="E73" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="F73" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G73" t="n">
+        <v>12</v>
+      </c>
+      <c r="H73" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I73" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J73" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="K73" t="n">
+        <v>10.5</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Table 4.7: Placement outcomes by level and pathway</t>
-        </is>
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>Died</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F74" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H74" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I74" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J74" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1.9</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>pathway_level</t>
-        </is>
-      </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="n"/>
-      <c r="D75" s="1" t="n"/>
-      <c r="E75" s="1" t="n"/>
-      <c r="F75" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G75" s="1" t="n"/>
-      <c r="H75" s="1" t="n"/>
-      <c r="I75" s="1" t="n"/>
-      <c r="J75" s="1" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K75" s="1" t="n"/>
-      <c r="L75" s="1" t="n"/>
-      <c r="M75" s="1" t="n"/>
-      <c r="N75" s="1" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O75" s="1" t="n"/>
-      <c r="P75" s="1" t="n"/>
-      <c r="Q75" s="1" t="n"/>
-      <c r="R75" s="1" t="inlineStr">
-        <is>
           <t>All</t>
         </is>
       </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="1" t="inlineStr">
-        <is>
-          <t>pathway_short</t>
-        </is>
-      </c>
-      <c r="B76" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C76" s="1" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="D76" s="1" t="inlineStr">
-        <is>
-          <t>M/F</t>
-        </is>
-      </c>
-      <c r="E76" s="1" t="inlineStr">
-        <is>
-          <t>SU</t>
-        </is>
-      </c>
-      <c r="F76" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="G76" s="1" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H76" s="1" t="inlineStr">
-        <is>
-          <t>M/F</t>
-        </is>
-      </c>
-      <c r="I76" s="1" t="inlineStr">
-        <is>
-          <t>SU</t>
-        </is>
-      </c>
-      <c r="J76" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="K76" s="1" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L76" s="1" t="inlineStr">
-        <is>
-          <t>M/F</t>
-        </is>
-      </c>
-      <c r="M76" s="1" t="inlineStr">
-        <is>
-          <t>SU</t>
-        </is>
-      </c>
-      <c r="N76" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="O76" s="1" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="P76" s="1" t="inlineStr">
-        <is>
-          <t>M/F</t>
-        </is>
-      </c>
-      <c r="Q76" s="1" t="inlineStr">
-        <is>
-          <t>SU</t>
-        </is>
-      </c>
-      <c r="R76" s="1" t="inlineStr"/>
+      <c r="B75" t="n">
+        <v>100</v>
+      </c>
+      <c r="C75" t="n">
+        <v>100</v>
+      </c>
+      <c r="D75" t="n">
+        <v>100</v>
+      </c>
+      <c r="E75" t="n">
+        <v>100</v>
+      </c>
+      <c r="F75" t="n">
+        <v>100</v>
+      </c>
+      <c r="G75" t="n">
+        <v>100</v>
+      </c>
+      <c r="H75" t="n">
+        <v>100</v>
+      </c>
+      <c r="I75" t="n">
+        <v>100</v>
+      </c>
+      <c r="J75" t="n">
+        <v>100</v>
+      </c>
+      <c r="K75" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="inlineStr">
-        <is>
-          <t>pl_outcome</t>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Table 4.7: Placement outcomes by level and pathway</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>Internal move: forwards</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>139</v>
-      </c>
-      <c r="C78" t="n">
-        <v>462</v>
-      </c>
-      <c r="D78" t="n">
-        <v>323</v>
-      </c>
-      <c r="E78" t="n">
-        <v>212</v>
-      </c>
-      <c r="F78" t="n">
-        <v>140</v>
-      </c>
-      <c r="G78" t="n">
-        <v>84</v>
-      </c>
-      <c r="H78" t="n">
-        <v>77</v>
-      </c>
-      <c r="I78" t="n">
-        <v>37</v>
-      </c>
-      <c r="J78" t="n">
-        <v>28</v>
-      </c>
-      <c r="K78" t="n">
-        <v>48</v>
-      </c>
-      <c r="L78" t="n">
-        <v>12</v>
-      </c>
-      <c r="M78" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" t="n">
-        <v>1562</v>
+          <t>pathway_level</t>
+        </is>
+      </c>
+      <c r="B78" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="n"/>
+      <c r="D78" s="1" t="n"/>
+      <c r="E78" s="1" t="n"/>
+      <c r="F78" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G78" s="1" t="n"/>
+      <c r="H78" s="1" t="n"/>
+      <c r="I78" s="1" t="n"/>
+      <c r="J78" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K78" s="1" t="n"/>
+      <c r="L78" s="1" t="n"/>
+      <c r="M78" s="1" t="n"/>
+      <c r="N78" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O78" s="1" t="n"/>
+      <c r="P78" s="1" t="n"/>
+      <c r="Q78" s="1" t="n"/>
+      <c r="R78" s="1" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>Independent accommodation</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>11</v>
-      </c>
-      <c r="C79" t="n">
-        <v>66</v>
-      </c>
-      <c r="D79" t="n">
-        <v>76</v>
-      </c>
-      <c r="E79" t="n">
-        <v>48</v>
-      </c>
-      <c r="F79" t="n">
-        <v>31</v>
-      </c>
-      <c r="G79" t="n">
-        <v>29</v>
-      </c>
-      <c r="H79" t="n">
-        <v>22</v>
-      </c>
-      <c r="I79" t="n">
-        <v>84</v>
-      </c>
-      <c r="J79" t="n">
-        <v>75</v>
-      </c>
-      <c r="K79" t="n">
-        <v>32</v>
-      </c>
-      <c r="L79" t="n">
-        <v>13</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" t="n">
-        <v>144</v>
-      </c>
-      <c r="O79" t="n">
-        <v>382</v>
-      </c>
-      <c r="P79" t="n">
-        <v>212</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
-      <c r="R79" t="n">
-        <v>1225</v>
-      </c>
+          <t>pathway_short</t>
+        </is>
+      </c>
+      <c r="B79" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D79" s="1" t="inlineStr">
+        <is>
+          <t>M/F</t>
+        </is>
+      </c>
+      <c r="E79" s="1" t="inlineStr">
+        <is>
+          <t>SU</t>
+        </is>
+      </c>
+      <c r="F79" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G79" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H79" s="1" t="inlineStr">
+        <is>
+          <t>M/F</t>
+        </is>
+      </c>
+      <c r="I79" s="1" t="inlineStr">
+        <is>
+          <t>SU</t>
+        </is>
+      </c>
+      <c r="J79" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="K79" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L79" s="1" t="inlineStr">
+        <is>
+          <t>M/F</t>
+        </is>
+      </c>
+      <c r="M79" s="1" t="inlineStr">
+        <is>
+          <t>SU</t>
+        </is>
+      </c>
+      <c r="N79" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O79" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P79" s="1" t="inlineStr">
+        <is>
+          <t>M/F</t>
+        </is>
+      </c>
+      <c r="Q79" s="1" t="inlineStr">
+        <is>
+          <t>SU</t>
+        </is>
+      </c>
+      <c r="R79" s="1" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>Internal move: sideways</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>71</v>
-      </c>
-      <c r="C80" t="n">
-        <v>326</v>
-      </c>
-      <c r="D80" t="n">
-        <v>308</v>
-      </c>
-      <c r="E80" t="n">
-        <v>342</v>
-      </c>
-      <c r="F80" t="n">
-        <v>37</v>
-      </c>
-      <c r="G80" t="n">
-        <v>8</v>
-      </c>
-      <c r="H80" t="n">
-        <v>23</v>
-      </c>
-      <c r="I80" t="n">
-        <v>4</v>
-      </c>
-      <c r="J80" t="n">
-        <v>7</v>
-      </c>
-      <c r="K80" t="n">
-        <v>1</v>
-      </c>
-      <c r="L80" t="n">
-        <v>4</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" t="n">
-        <v>8</v>
-      </c>
-      <c r="O80" t="n">
-        <v>19</v>
-      </c>
-      <c r="P80" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
-      <c r="R80" t="n">
-        <v>1164</v>
+          <t>pl_outcome</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>Returned to homelessness</t>
+          <t>Internal move: forwards</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>32</v>
+        <v>139</v>
       </c>
       <c r="C81" t="n">
-        <v>215</v>
+        <v>462</v>
       </c>
       <c r="D81" t="n">
-        <v>115</v>
+        <v>323</v>
       </c>
       <c r="E81" t="n">
-        <v>168</v>
+        <v>212</v>
       </c>
       <c r="F81" t="n">
-        <v>36</v>
+        <v>140</v>
       </c>
       <c r="G81" t="n">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="H81" t="n">
+        <v>77</v>
+      </c>
+      <c r="I81" t="n">
+        <v>37</v>
+      </c>
+      <c r="J81" t="n">
+        <v>28</v>
+      </c>
+      <c r="K81" t="n">
+        <v>48</v>
+      </c>
+      <c r="L81" t="n">
         <v>12</v>
       </c>
-      <c r="I81" t="n">
-        <v>21</v>
-      </c>
-      <c r="J81" t="n">
-        <v>19</v>
-      </c>
-      <c r="K81" t="n">
-        <v>8</v>
-      </c>
-      <c r="L81" t="n">
-        <v>4</v>
-      </c>
       <c r="M81" t="n">
         <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>744</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>Internal move: backwards</t>
+          <t>Independent accommodation</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="F82" t="n">
-        <v>89</v>
+        <v>31</v>
       </c>
       <c r="G82" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="H82" t="n">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="I82" t="n">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="J82" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="K82" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="L82" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>31</v>
+        <v>144</v>
       </c>
       <c r="O82" t="n">
-        <v>110</v>
+        <v>382</v>
       </c>
       <c r="P82" t="n">
-        <v>50</v>
+        <v>212</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>653</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>Insecure outcome</t>
+          <t>Internal move: sideways</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="C83" t="n">
-        <v>139</v>
+        <v>326</v>
       </c>
       <c r="D83" t="n">
-        <v>114</v>
+        <v>308</v>
       </c>
       <c r="E83" t="n">
-        <v>96</v>
+        <v>342</v>
       </c>
       <c r="F83" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G83" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H83" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I83" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="J83" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="K83" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L83" t="n">
         <v>4</v>
@@ -2681,1343 +2570,1517 @@
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="O83" t="n">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="P83" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>638</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>Died</t>
+          <t>Returned to homelessness</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="C84" t="n">
-        <v>29</v>
+        <v>215</v>
       </c>
       <c r="D84" t="n">
+        <v>115</v>
+      </c>
+      <c r="E84" t="n">
+        <v>168</v>
+      </c>
+      <c r="F84" t="n">
+        <v>36</v>
+      </c>
+      <c r="G84" t="n">
+        <v>22</v>
+      </c>
+      <c r="H84" t="n">
+        <v>12</v>
+      </c>
+      <c r="I84" t="n">
+        <v>21</v>
+      </c>
+      <c r="J84" t="n">
+        <v>19</v>
+      </c>
+      <c r="K84" t="n">
+        <v>8</v>
+      </c>
+      <c r="L84" t="n">
+        <v>4</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="n">
+        <v>22</v>
+      </c>
+      <c r="O84" t="n">
+        <v>53</v>
+      </c>
+      <c r="P84" t="n">
         <v>17</v>
       </c>
-      <c r="E84" t="n">
-        <v>14</v>
-      </c>
-      <c r="F84" t="n">
-        <v>6</v>
-      </c>
-      <c r="G84" t="n">
-        <v>7</v>
-      </c>
-      <c r="H84" t="n">
-        <v>6</v>
-      </c>
-      <c r="I84" t="n">
-        <v>2</v>
-      </c>
-      <c r="J84" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" t="n">
-        <v>9</v>
-      </c>
-      <c r="L84" t="n">
-        <v>2</v>
-      </c>
-      <c r="M84" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" t="n">
-        <v>1</v>
-      </c>
-      <c r="O84" t="n">
-        <v>11</v>
-      </c>
-      <c r="P84" t="n">
-        <v>11</v>
-      </c>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>117</v>
+        <v>744</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Internal move: backwards</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>286</v>
+        <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>1237</v>
+        <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>953</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>880</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>377</v>
+        <v>89</v>
       </c>
       <c r="G85" t="n">
-        <v>227</v>
+        <v>55</v>
       </c>
       <c r="H85" t="n">
-        <v>239</v>
+        <v>74</v>
       </c>
       <c r="I85" t="n">
-        <v>301</v>
+        <v>128</v>
       </c>
       <c r="J85" t="n">
-        <v>194</v>
+        <v>46</v>
       </c>
       <c r="K85" t="n">
-        <v>154</v>
+        <v>44</v>
       </c>
       <c r="L85" t="n">
-        <v>65</v>
-      </c>
-      <c r="M85" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
       <c r="N85" t="n">
-        <v>232</v>
+        <v>31</v>
       </c>
       <c r="O85" t="n">
-        <v>641</v>
+        <v>110</v>
       </c>
       <c r="P85" t="n">
-        <v>317</v>
-      </c>
-      <c r="Q85" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
       <c r="R85" t="n">
-        <v>6103</v>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>Insecure outcome</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>31</v>
+      </c>
+      <c r="C86" t="n">
+        <v>139</v>
+      </c>
+      <c r="D86" t="n">
+        <v>114</v>
+      </c>
+      <c r="E86" t="n">
+        <v>96</v>
+      </c>
+      <c r="F86" t="n">
+        <v>38</v>
+      </c>
+      <c r="G86" t="n">
+        <v>22</v>
+      </c>
+      <c r="H86" t="n">
+        <v>25</v>
+      </c>
+      <c r="I86" t="n">
+        <v>25</v>
+      </c>
+      <c r="J86" t="n">
+        <v>19</v>
+      </c>
+      <c r="K86" t="n">
+        <v>12</v>
+      </c>
+      <c r="L86" t="n">
+        <v>4</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="n">
+        <v>26</v>
+      </c>
+      <c r="O86" t="n">
+        <v>66</v>
+      </c>
+      <c r="P86" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" t="n">
+        <v>638</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Table 4.8: Placement outcomes (as row percentages) by level and pathway</t>
-        </is>
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>Died</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>2</v>
+      </c>
+      <c r="C87" t="n">
+        <v>29</v>
+      </c>
+      <c r="D87" t="n">
+        <v>17</v>
+      </c>
+      <c r="E87" t="n">
+        <v>14</v>
+      </c>
+      <c r="F87" t="n">
+        <v>6</v>
+      </c>
+      <c r="G87" t="n">
+        <v>7</v>
+      </c>
+      <c r="H87" t="n">
+        <v>6</v>
+      </c>
+      <c r="I87" t="n">
+        <v>2</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>9</v>
+      </c>
+      <c r="L87" t="n">
+        <v>2</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>1</v>
+      </c>
+      <c r="O87" t="n">
+        <v>11</v>
+      </c>
+      <c r="P87" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>117</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>pathway_level</t>
-        </is>
-      </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="n"/>
-      <c r="D88" s="1" t="n"/>
-      <c r="E88" s="1" t="n"/>
-      <c r="F88" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G88" s="1" t="n"/>
-      <c r="H88" s="1" t="n"/>
-      <c r="I88" s="1" t="n"/>
-      <c r="J88" s="1" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K88" s="1" t="n"/>
-      <c r="L88" s="1" t="n"/>
-      <c r="M88" s="1" t="n"/>
-      <c r="N88" s="1" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O88" s="1" t="n"/>
-      <c r="P88" s="1" t="n"/>
-      <c r="Q88" s="1" t="n"/>
-      <c r="R88" s="1" t="inlineStr">
-        <is>
           <t>All</t>
         </is>
       </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="1" t="inlineStr">
-        <is>
-          <t>pathway_short</t>
-        </is>
-      </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>M/F</t>
-        </is>
-      </c>
-      <c r="E89" s="1" t="inlineStr">
-        <is>
-          <t>SU</t>
-        </is>
-      </c>
-      <c r="F89" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="G89" s="1" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H89" s="1" t="inlineStr">
-        <is>
-          <t>M/F</t>
-        </is>
-      </c>
-      <c r="I89" s="1" t="inlineStr">
-        <is>
-          <t>SU</t>
-        </is>
-      </c>
-      <c r="J89" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="K89" s="1" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L89" s="1" t="inlineStr">
-        <is>
-          <t>M/F</t>
-        </is>
-      </c>
-      <c r="M89" s="1" t="inlineStr">
-        <is>
-          <t>SU</t>
-        </is>
-      </c>
-      <c r="N89" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="O89" s="1" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="P89" s="1" t="inlineStr">
-        <is>
-          <t>M/F</t>
-        </is>
-      </c>
-      <c r="Q89" s="1" t="inlineStr">
-        <is>
-          <t>SU</t>
-        </is>
-      </c>
-      <c r="R89" s="1" t="inlineStr"/>
+      <c r="B88" t="n">
+        <v>286</v>
+      </c>
+      <c r="C88" t="n">
+        <v>1237</v>
+      </c>
+      <c r="D88" t="n">
+        <v>953</v>
+      </c>
+      <c r="E88" t="n">
+        <v>880</v>
+      </c>
+      <c r="F88" t="n">
+        <v>377</v>
+      </c>
+      <c r="G88" t="n">
+        <v>227</v>
+      </c>
+      <c r="H88" t="n">
+        <v>239</v>
+      </c>
+      <c r="I88" t="n">
+        <v>301</v>
+      </c>
+      <c r="J88" t="n">
+        <v>194</v>
+      </c>
+      <c r="K88" t="n">
+        <v>154</v>
+      </c>
+      <c r="L88" t="n">
+        <v>65</v>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="n">
+        <v>232</v>
+      </c>
+      <c r="O88" t="n">
+        <v>641</v>
+      </c>
+      <c r="P88" t="n">
+        <v>317</v>
+      </c>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="n">
+        <v>6103</v>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="inlineStr">
-        <is>
-          <t>pl_outcome</t>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Table 4.8: Placement outcomes (as row percentages) by level and pathway</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>Internal move: forwards</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="C91" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="D91" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="E91" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="F91" t="n">
-        <v>37.1</v>
-      </c>
-      <c r="G91" t="n">
-        <v>37</v>
-      </c>
-      <c r="H91" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="I91" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="J91" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="K91" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="L91" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="n">
-        <v>25.6</v>
+          <t>pathway_level</t>
+        </is>
+      </c>
+      <c r="B91" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C91" s="1" t="n"/>
+      <c r="D91" s="1" t="n"/>
+      <c r="E91" s="1" t="n"/>
+      <c r="F91" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G91" s="1" t="n"/>
+      <c r="H91" s="1" t="n"/>
+      <c r="I91" s="1" t="n"/>
+      <c r="J91" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K91" s="1" t="n"/>
+      <c r="L91" s="1" t="n"/>
+      <c r="M91" s="1" t="n"/>
+      <c r="N91" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O91" s="1" t="n"/>
+      <c r="P91" s="1" t="n"/>
+      <c r="Q91" s="1" t="n"/>
+      <c r="R91" s="1" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>Independent accommodation</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="C92" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="D92" t="n">
-        <v>8</v>
-      </c>
-      <c r="E92" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F92" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="G92" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="H92" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="I92" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="J92" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="K92" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="L92" t="n">
-        <v>20</v>
-      </c>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="O92" t="n">
-        <v>59.6</v>
-      </c>
-      <c r="P92" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="n">
-        <v>20.1</v>
-      </c>
+          <t>pathway_short</t>
+        </is>
+      </c>
+      <c r="B92" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D92" s="1" t="inlineStr">
+        <is>
+          <t>M/F</t>
+        </is>
+      </c>
+      <c r="E92" s="1" t="inlineStr">
+        <is>
+          <t>SU</t>
+        </is>
+      </c>
+      <c r="F92" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G92" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H92" s="1" t="inlineStr">
+        <is>
+          <t>M/F</t>
+        </is>
+      </c>
+      <c r="I92" s="1" t="inlineStr">
+        <is>
+          <t>SU</t>
+        </is>
+      </c>
+      <c r="J92" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="K92" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L92" s="1" t="inlineStr">
+        <is>
+          <t>M/F</t>
+        </is>
+      </c>
+      <c r="M92" s="1" t="inlineStr">
+        <is>
+          <t>SU</t>
+        </is>
+      </c>
+      <c r="N92" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O92" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P92" s="1" t="inlineStr">
+        <is>
+          <t>M/F</t>
+        </is>
+      </c>
+      <c r="Q92" s="1" t="inlineStr">
+        <is>
+          <t>SU</t>
+        </is>
+      </c>
+      <c r="R92" s="1" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>Internal move: sideways</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="C93" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="D93" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="E93" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="F93" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="G93" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H93" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="I93" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J93" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K93" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L93" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O93" t="n">
-        <v>3</v>
-      </c>
-      <c r="P93" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="n">
-        <v>19.1</v>
+          <t>pl_outcome</t>
+        </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>Returned to homelessness</t>
+          <t>Internal move: forwards</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>11.2</v>
+        <v>48.6</v>
       </c>
       <c r="C94" t="n">
-        <v>17.4</v>
+        <v>37.3</v>
       </c>
       <c r="D94" t="n">
-        <v>12.1</v>
+        <v>33.9</v>
       </c>
       <c r="E94" t="n">
-        <v>19.1</v>
+        <v>24.1</v>
       </c>
       <c r="F94" t="n">
-        <v>9.5</v>
+        <v>37.1</v>
       </c>
       <c r="G94" t="n">
-        <v>9.699999999999999</v>
+        <v>37</v>
       </c>
       <c r="H94" t="n">
-        <v>5</v>
+        <v>32.2</v>
       </c>
       <c r="I94" t="n">
-        <v>7</v>
+        <v>12.3</v>
       </c>
       <c r="J94" t="n">
-        <v>9.800000000000001</v>
+        <v>14.4</v>
       </c>
       <c r="K94" t="n">
-        <v>5.2</v>
+        <v>31.2</v>
       </c>
       <c r="L94" t="n">
-        <v>6.2</v>
+        <v>18.5</v>
       </c>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="n">
-        <v>12.2</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>Internal move: backwards</t>
+          <t>Independent accommodation</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="F95" t="n">
-        <v>23.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G95" t="n">
-        <v>24.2</v>
+        <v>12.8</v>
       </c>
       <c r="H95" t="n">
-        <v>31</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I95" t="n">
-        <v>42.5</v>
+        <v>27.9</v>
       </c>
       <c r="J95" t="n">
-        <v>23.7</v>
+        <v>38.7</v>
       </c>
       <c r="K95" t="n">
-        <v>28.6</v>
+        <v>20.8</v>
       </c>
       <c r="L95" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="n">
-        <v>13.4</v>
+        <v>62.1</v>
       </c>
       <c r="O95" t="n">
-        <v>17.2</v>
+        <v>59.6</v>
       </c>
       <c r="P95" t="n">
-        <v>15.8</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="n">
-        <v>10.7</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>Insecure outcome</t>
+          <t>Internal move: sideways</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>10.8</v>
+        <v>24.8</v>
       </c>
       <c r="C96" t="n">
-        <v>11.2</v>
+        <v>26.4</v>
       </c>
       <c r="D96" t="n">
-        <v>12</v>
+        <v>32.3</v>
       </c>
       <c r="E96" t="n">
-        <v>10.9</v>
+        <v>38.9</v>
       </c>
       <c r="F96" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G96" t="n">
-        <v>9.699999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="H96" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="I96" t="n">
-        <v>8.300000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="J96" t="n">
-        <v>9.800000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="K96" t="n">
-        <v>7.8</v>
+        <v>0.6</v>
       </c>
       <c r="L96" t="n">
         <v>6.2</v>
       </c>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="n">
-        <v>11.2</v>
+        <v>3.4</v>
       </c>
       <c r="O96" t="n">
-        <v>10.3</v>
+        <v>3</v>
       </c>
       <c r="P96" t="n">
-        <v>6.6</v>
+        <v>1.9</v>
       </c>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="n">
-        <v>10.5</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>Died</t>
+          <t>Returned to homelessness</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.7</v>
+        <v>11.2</v>
       </c>
       <c r="C97" t="n">
-        <v>2.3</v>
+        <v>17.4</v>
       </c>
       <c r="D97" t="n">
-        <v>1.8</v>
+        <v>12.1</v>
       </c>
       <c r="E97" t="n">
-        <v>1.6</v>
+        <v>19.1</v>
       </c>
       <c r="F97" t="n">
-        <v>1.6</v>
+        <v>9.5</v>
       </c>
       <c r="G97" t="n">
-        <v>3.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H97" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="I97" t="n">
-        <v>0.7</v>
+        <v>7</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K97" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="L97" t="n">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="n">
-        <v>0.4</v>
+        <v>9.5</v>
       </c>
       <c r="O97" t="n">
-        <v>1.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P97" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="n">
-        <v>1.9</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Internal move: backwards</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>100</v>
+        <v>23.6</v>
       </c>
       <c r="G98" t="n">
-        <v>100</v>
+        <v>24.2</v>
       </c>
       <c r="H98" t="n">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="I98" t="n">
-        <v>100</v>
+        <v>42.5</v>
       </c>
       <c r="J98" t="n">
-        <v>100</v>
+        <v>23.7</v>
       </c>
       <c r="K98" t="n">
-        <v>100</v>
+        <v>28.6</v>
       </c>
       <c r="L98" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="n">
-        <v>100</v>
+        <v>13.4</v>
       </c>
       <c r="O98" t="n">
-        <v>100</v>
+        <v>17.2</v>
       </c>
       <c r="P98" t="n">
-        <v>100</v>
+        <v>15.8</v>
       </c>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="n">
-        <v>100</v>
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>Insecure outcome</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="C99" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="D99" t="n">
+        <v>12</v>
+      </c>
+      <c r="E99" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F99" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="G99" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H99" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I99" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J99" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="K99" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L99" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="O99" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="P99" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="n">
+        <v>10.5</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Table 4.9: Placement outcomes from level 3-4 by shared vs. self-contained</t>
-        </is>
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>Died</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C100" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D100" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G100" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H100" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L100" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O100" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P100" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="n">
+        <v>1.9</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>shared</t>
-        </is>
-      </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>Self-contained</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="n"/>
-      <c r="D101" s="1" t="n"/>
-      <c r="E101" s="1" t="inlineStr">
-        <is>
-          <t>Shared</t>
-        </is>
-      </c>
-      <c r="F101" s="1" t="n"/>
-      <c r="G101" s="1" t="n"/>
-      <c r="H101" s="1" t="inlineStr">
-        <is>
           <t>All</t>
         </is>
       </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="1" t="inlineStr">
-        <is>
-          <t>pathway_short</t>
-        </is>
-      </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>M/F</t>
-        </is>
-      </c>
-      <c r="E102" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F102" s="1" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G102" s="1" t="inlineStr">
-        <is>
-          <t>M/F</t>
-        </is>
-      </c>
-      <c r="H102" s="1" t="inlineStr"/>
+      <c r="B101" t="n">
+        <v>100</v>
+      </c>
+      <c r="C101" t="n">
+        <v>100</v>
+      </c>
+      <c r="D101" t="n">
+        <v>100</v>
+      </c>
+      <c r="E101" t="n">
+        <v>100</v>
+      </c>
+      <c r="F101" t="n">
+        <v>100</v>
+      </c>
+      <c r="G101" t="n">
+        <v>100</v>
+      </c>
+      <c r="H101" t="n">
+        <v>100</v>
+      </c>
+      <c r="I101" t="n">
+        <v>100</v>
+      </c>
+      <c r="J101" t="n">
+        <v>100</v>
+      </c>
+      <c r="K101" t="n">
+        <v>100</v>
+      </c>
+      <c r="L101" t="n">
+        <v>100</v>
+      </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="n">
+        <v>100</v>
+      </c>
+      <c r="O101" t="n">
+        <v>100</v>
+      </c>
+      <c r="P101" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="inlineStr">
-        <is>
-          <t>pl_outcome</t>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Table 4.9: Placement outcomes from level 3-4 by shared vs. self-contained</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>Independent accommodation</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>200</v>
-      </c>
-      <c r="C104" t="n">
-        <v>352</v>
-      </c>
-      <c r="D104" t="n">
-        <v>223</v>
-      </c>
-      <c r="E104" t="n">
-        <v>19</v>
-      </c>
-      <c r="F104" t="n">
-        <v>62</v>
-      </c>
-      <c r="G104" t="n">
-        <v>2</v>
-      </c>
-      <c r="H104" t="n">
-        <v>858</v>
+          <t>shared</t>
+        </is>
+      </c>
+      <c r="B104" s="1" t="inlineStr">
+        <is>
+          <t>Self-contained</t>
+        </is>
+      </c>
+      <c r="C104" s="1" t="n"/>
+      <c r="D104" s="1" t="n"/>
+      <c r="E104" s="1" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="F104" s="1" t="n"/>
+      <c r="G104" s="1" t="n"/>
+      <c r="H104" s="1" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>Internal move: backwards</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
-        <v>65</v>
-      </c>
-      <c r="C105" t="n">
-        <v>130</v>
-      </c>
-      <c r="D105" t="n">
-        <v>70</v>
-      </c>
-      <c r="E105" t="n">
-        <v>12</v>
-      </c>
-      <c r="F105" t="n">
-        <v>24</v>
-      </c>
-      <c r="G105" t="n">
-        <v>6</v>
-      </c>
-      <c r="H105" t="n">
-        <v>307</v>
-      </c>
+          <t>pathway_short</t>
+        </is>
+      </c>
+      <c r="B105" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D105" s="1" t="inlineStr">
+        <is>
+          <t>M/F</t>
+        </is>
+      </c>
+      <c r="E105" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F105" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G105" s="1" t="inlineStr">
+        <is>
+          <t>M/F</t>
+        </is>
+      </c>
+      <c r="H105" s="1" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>Insecure outcome</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
-        <v>40</v>
-      </c>
-      <c r="C106" t="n">
-        <v>58</v>
-      </c>
-      <c r="D106" t="n">
-        <v>24</v>
-      </c>
-      <c r="E106" t="n">
-        <v>5</v>
-      </c>
-      <c r="F106" t="n">
-        <v>20</v>
-      </c>
-      <c r="G106" t="n">
-        <v>1</v>
-      </c>
-      <c r="H106" t="n">
-        <v>148</v>
+          <t>pl_outcome</t>
+        </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>Returned to homelessness</t>
+          <t>Independent accommodation</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>35</v>
+        <v>200</v>
       </c>
       <c r="C107" t="n">
-        <v>50</v>
+        <v>352</v>
       </c>
       <c r="D107" t="n">
-        <v>20</v>
+        <v>223</v>
       </c>
       <c r="E107" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F107" t="n">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="G107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H107" t="n">
-        <v>123</v>
+        <v>858</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>Internal move: forwards</t>
+          <t>Internal move: backwards</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="C108" t="n">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="D108" t="n">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="E108" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="G108" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H108" t="n">
-        <v>88</v>
+        <v>307</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>Internal move: sideways</t>
+          <t>Insecure outcome</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="C109" t="n">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="D109" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E109" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="G109" t="n">
         <v>1</v>
       </c>
       <c r="H109" t="n">
-        <v>45</v>
+        <v>148</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>Died</t>
+          <t>Returned to homelessness</t>
         </is>
       </c>
       <c r="B110" t="n">
+        <v>35</v>
+      </c>
+      <c r="C110" t="n">
+        <v>50</v>
+      </c>
+      <c r="D110" t="n">
+        <v>20</v>
+      </c>
+      <c r="E110" t="n">
+        <v>6</v>
+      </c>
+      <c r="F110" t="n">
+        <v>11</v>
+      </c>
+      <c r="G110" t="n">
         <v>1</v>
       </c>
-      <c r="C110" t="n">
-        <v>19</v>
-      </c>
-      <c r="D110" t="n">
-        <v>13</v>
-      </c>
-      <c r="E110" t="n">
-        <v>0</v>
-      </c>
-      <c r="F110" t="n">
-        <v>1</v>
-      </c>
-      <c r="G110" t="n">
-        <v>0</v>
-      </c>
       <c r="H110" t="n">
-        <v>34</v>
+        <v>123</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Internal move: forwards</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>380</v>
+        <v>27</v>
       </c>
       <c r="C111" t="n">
-        <v>672</v>
+        <v>46</v>
       </c>
       <c r="D111" t="n">
-        <v>368</v>
+        <v>9</v>
       </c>
       <c r="E111" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="F111" t="n">
-        <v>123</v>
+        <v>2</v>
       </c>
       <c r="G111" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H111" t="n">
-        <v>1603</v>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>Internal move: sideways</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>12</v>
+      </c>
+      <c r="C112" t="n">
+        <v>17</v>
+      </c>
+      <c r="D112" t="n">
+        <v>9</v>
+      </c>
+      <c r="E112" t="n">
+        <v>3</v>
+      </c>
+      <c r="F112" t="n">
+        <v>3</v>
+      </c>
+      <c r="G112" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Table 4.10: Placement outcomes (as row percentages) from level 3-4 by shared vs. self-contained</t>
-        </is>
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>Died</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" t="n">
+        <v>19</v>
+      </c>
+      <c r="D113" t="n">
+        <v>13</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>shared</t>
-        </is>
-      </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>Self-contained %</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="n"/>
-      <c r="D114" s="1" t="n"/>
-      <c r="E114" s="1" t="inlineStr">
-        <is>
-          <t>Shared %</t>
-        </is>
-      </c>
-      <c r="F114" s="1" t="n"/>
-      <c r="G114" s="1" t="n"/>
-      <c r="H114" s="1" t="inlineStr">
-        <is>
-          <t>All %</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="1" t="inlineStr">
-        <is>
-          <t>pathway_short</t>
-        </is>
-      </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>F %</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>M %</t>
-        </is>
-      </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>M/F %</t>
-        </is>
-      </c>
-      <c r="E115" s="1" t="inlineStr">
-        <is>
-          <t>F %</t>
-        </is>
-      </c>
-      <c r="F115" s="1" t="inlineStr">
-        <is>
-          <t>M %</t>
-        </is>
-      </c>
-      <c r="G115" s="1" t="inlineStr">
-        <is>
-          <t>M/F %</t>
-        </is>
-      </c>
-      <c r="H115" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> %</t>
-        </is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>380</v>
+      </c>
+      <c r="C114" t="n">
+        <v>672</v>
+      </c>
+      <c r="D114" t="n">
+        <v>368</v>
+      </c>
+      <c r="E114" t="n">
+        <v>46</v>
+      </c>
+      <c r="F114" t="n">
+        <v>123</v>
+      </c>
+      <c r="G114" t="n">
+        <v>14</v>
+      </c>
+      <c r="H114" t="n">
+        <v>1603</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="inlineStr">
-        <is>
-          <t>pl_outcome</t>
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Table 4.10: Placement outcomes (as row percentages) from level 3-4 by shared vs. self-contained</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>Independent accommodation</t>
-        </is>
-      </c>
-      <c r="B117" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="C117" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="D117" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="E117" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="F117" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="G117" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="H117" t="n">
-        <v>53.5</v>
+          <t>shared</t>
+        </is>
+      </c>
+      <c r="B117" s="1" t="inlineStr">
+        <is>
+          <t>Self-contained %</t>
+        </is>
+      </c>
+      <c r="C117" s="1" t="n"/>
+      <c r="D117" s="1" t="n"/>
+      <c r="E117" s="1" t="inlineStr">
+        <is>
+          <t>Shared %</t>
+        </is>
+      </c>
+      <c r="F117" s="1" t="n"/>
+      <c r="G117" s="1" t="n"/>
+      <c r="H117" s="1" t="inlineStr">
+        <is>
+          <t>All %</t>
+        </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>Internal move: backwards</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="C118" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="D118" t="n">
-        <v>19</v>
-      </c>
-      <c r="E118" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="F118" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="G118" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="H118" t="n">
-        <v>19.2</v>
+          <t>pathway_short</t>
+        </is>
+      </c>
+      <c r="B118" s="1" t="inlineStr">
+        <is>
+          <t>F %</t>
+        </is>
+      </c>
+      <c r="C118" s="1" t="inlineStr">
+        <is>
+          <t>M %</t>
+        </is>
+      </c>
+      <c r="D118" s="1" t="inlineStr">
+        <is>
+          <t>M/F %</t>
+        </is>
+      </c>
+      <c r="E118" s="1" t="inlineStr">
+        <is>
+          <t>F %</t>
+        </is>
+      </c>
+      <c r="F118" s="1" t="inlineStr">
+        <is>
+          <t>M %</t>
+        </is>
+      </c>
+      <c r="G118" s="1" t="inlineStr">
+        <is>
+          <t>M/F %</t>
+        </is>
+      </c>
+      <c r="H118" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> %</t>
+        </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>Insecure outcome</t>
-        </is>
-      </c>
-      <c r="B119" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="C119" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="D119" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E119" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="F119" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="G119" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="H119" t="n">
-        <v>9.199999999999999</v>
+          <t>pl_outcome</t>
+        </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>Returned to homelessness</t>
+          <t>Independent accommodation</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>9.199999999999999</v>
+        <v>52.6</v>
       </c>
       <c r="C120" t="n">
-        <v>7.4</v>
+        <v>52.4</v>
       </c>
       <c r="D120" t="n">
-        <v>5.4</v>
+        <v>60.6</v>
       </c>
       <c r="E120" t="n">
-        <v>13</v>
+        <v>41.3</v>
       </c>
       <c r="F120" t="n">
-        <v>8.9</v>
+        <v>50.4</v>
       </c>
       <c r="G120" t="n">
-        <v>7.1</v>
+        <v>14.3</v>
       </c>
       <c r="H120" t="n">
-        <v>7.7</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>Internal move: forwards</t>
+          <t>Internal move: backwards</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>7.1</v>
+        <v>17.1</v>
       </c>
       <c r="C121" t="n">
-        <v>6.8</v>
+        <v>19.3</v>
       </c>
       <c r="D121" t="n">
-        <v>2.4</v>
+        <v>19</v>
       </c>
       <c r="E121" t="n">
-        <v>2.2</v>
+        <v>26.1</v>
       </c>
       <c r="F121" t="n">
-        <v>1.6</v>
+        <v>19.5</v>
       </c>
       <c r="G121" t="n">
-        <v>21.4</v>
+        <v>42.9</v>
       </c>
       <c r="H121" t="n">
-        <v>5.5</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>Internal move: sideways</t>
+          <t>Insecure outcome</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>3.2</v>
+        <v>10.5</v>
       </c>
       <c r="C122" t="n">
-        <v>2.5</v>
+        <v>8.6</v>
       </c>
       <c r="D122" t="n">
-        <v>2.4</v>
+        <v>6.5</v>
       </c>
       <c r="E122" t="n">
-        <v>6.5</v>
+        <v>10.9</v>
       </c>
       <c r="F122" t="n">
-        <v>2.4</v>
+        <v>16.3</v>
       </c>
       <c r="G122" t="n">
         <v>7.1</v>
       </c>
       <c r="H122" t="n">
-        <v>2.8</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>Died</t>
+          <t>Returned to homelessness</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="C123" t="n">
-        <v>2.8</v>
+        <v>7.4</v>
       </c>
       <c r="D123" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="E123" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F123" t="n">
-        <v>0.8</v>
+        <v>8.9</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="H123" t="n">
-        <v>2.1</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
+          <t>Internal move: forwards</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C124" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D124" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E124" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G124" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="H124" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>Internal move: sideways</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C125" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D125" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E125" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F125" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G125" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H125" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>Died</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C126" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D126" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B124" t="n">
+      <c r="B127" t="n">
         <v>100</v>
       </c>
-      <c r="C124" t="n">
+      <c r="C127" t="n">
         <v>100</v>
       </c>
-      <c r="D124" t="n">
+      <c r="D127" t="n">
         <v>100</v>
       </c>
-      <c r="E124" t="n">
+      <c r="E127" t="n">
         <v>100</v>
       </c>
-      <c r="F124" t="n">
+      <c r="F127" t="n">
         <v>100</v>
       </c>
-      <c r="G124" t="n">
+      <c r="G127" t="n">
         <v>100</v>
       </c>
-      <c r="H124" t="n">
+      <c r="H127" t="n">
         <v>100</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="J75:M75"/>
+    <mergeCell ref="J91:M91"/>
     <mergeCell ref="A9:A14"/>
-    <mergeCell ref="F27:I27"/>
-    <mergeCell ref="N88:Q88"/>
-    <mergeCell ref="B101:D101"/>
+    <mergeCell ref="N78:Q78"/>
     <mergeCell ref="B3:B6"/>
-    <mergeCell ref="E114:G114"/>
-    <mergeCell ref="F88:I88"/>
-    <mergeCell ref="B75:E75"/>
+    <mergeCell ref="E104:G104"/>
     <mergeCell ref="B13:B14"/>
-    <mergeCell ref="E101:G101"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="F40:I40"/>
-    <mergeCell ref="N75:Q75"/>
-    <mergeCell ref="J88:M88"/>
+    <mergeCell ref="B91:E91"/>
+    <mergeCell ref="F78:I78"/>
+    <mergeCell ref="N91:Q91"/>
+    <mergeCell ref="B104:D104"/>
     <mergeCell ref="B9:B12"/>
     <mergeCell ref="A3:A8"/>
-    <mergeCell ref="B114:D114"/>
-    <mergeCell ref="F75:I75"/>
-    <mergeCell ref="B88:E88"/>
+    <mergeCell ref="J78:M78"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="F42:I42"/>
+    <mergeCell ref="E117:G117"/>
+    <mergeCell ref="F91:I91"/>
+    <mergeCell ref="B78:E78"/>
     <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="B117:D117"/>
+    <mergeCell ref="F28:I28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
